--- a/1. Reporting_Data/IB_Mark-to-Market PnL/AssetCurrency/2025/202511/Currency_P&L_20251107.xlsx
+++ b/1. Reporting_Data/IB_Mark-to-Market PnL/AssetCurrency/2025/202511/Currency_P&L_20251107.xlsx
@@ -23773,7 +23773,7 @@
         <v>45968</v>
       </c>
       <c r="B992">
-        <v>82851817.20999999</v>
+        <v>106875110</v>
       </c>
       <c r="C992">
         <v>-104338.94</v>
@@ -23782,10 +23782,10 @@
         <v>-0.0009790000000000001</v>
       </c>
       <c r="E992">
-        <v>447873.6</v>
+        <v>462564.4</v>
       </c>
       <c r="F992">
-        <v>0.0042</v>
+        <v>0.004338</v>
       </c>
       <c r="O992">
         <v>-88109.67999999999</v>
